--- a/backend/data/interns.xlsx
+++ b/backend/data/interns.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,104 +416,61 @@
         <v>password</v>
       </c>
       <c r="F1" t="str">
+        <v>createdBy</v>
+      </c>
+      <c r="G1" t="str">
         <v>createdAt</v>
-      </c>
-      <c r="G1" t="str">
-        <v>createdBy</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>INT001</v>
+        <v>T1945</v>
       </c>
       <c r="B2" t="str">
-        <v>Test Intern</v>
+        <v>HarshadNani</v>
       </c>
       <c r="C2" t="str">
-        <v>testintern</v>
+        <v>jeevan@gmail.com</v>
       </c>
       <c r="D2" t="str">
-        <v>9876543210</v>
+        <v>6301060151</v>
       </c>
       <c r="E2" t="str">
-        <v>$2b$10$K3vgIUHjDSWdCDoeuCZK5.4NtJg1crzrWrIvKZbJezct0bKLq1yUa</v>
+        <v>$2b$10$Suii6m15ZLn4lAqBQs7qK.Obpy8ToQRY5//E91j7vi4RyHdJwLwBO</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-10-21T12:45:26.610Z</v>
+        <v>68f768c7c19182865690172b</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-10-21T14:17:39.196Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>T1945</v>
+        <v>1940</v>
       </c>
       <c r="B3" t="str">
-        <v>HarshadNani</v>
+        <v>deepak</v>
       </c>
       <c r="C3" t="str">
-        <v>jeevan@gmail.com</v>
+        <v>deepak</v>
       </c>
       <c r="D3" t="str">
-        <v>6301060151</v>
+        <v>7995406088</v>
       </c>
       <c r="E3" t="str">
-        <v>$2b$10$Suii6m15ZLn4lAqBQs7qK.Obpy8ToQRY5//E91j7vi4RyHdJwLwBO</v>
+        <v>$2b$10$zVhso2YMCBHmc/TtkJMmbuZDMmrr3UEsE5XxG4tzNM9nXgU/T4R0q</v>
       </c>
       <c r="F3" t="str">
-        <v>2025-10-21T14:17:39.196Z</v>
+        <v>68f75dcdd8f6e3160c92371e</v>
       </c>
       <c r="G3" t="str">
-        <v>68f768c7c19182865690172b</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>1940</v>
-      </c>
-      <c r="B4" t="str">
-        <v>deepak</v>
-      </c>
-      <c r="C4" t="str">
-        <v>deepak</v>
-      </c>
-      <c r="D4" t="str">
-        <v>7995406088</v>
-      </c>
-      <c r="E4" t="str">
-        <v>$2b$10$zVhso2YMCBHmc/TtkJMmbuZDMmrr3UEsE5XxG4tzNM9nXgU/T4R0q</v>
-      </c>
-      <c r="F4" t="str">
         <v>2025-10-22T04:22:06.289Z</v>
-      </c>
-      <c r="G4" t="str">
-        <v>68f75dcdd8f6e3160c92371e</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>195</v>
-      </c>
-      <c r="B5" t="str">
-        <v>bal</v>
-      </c>
-      <c r="C5" t="str">
-        <v>bal</v>
-      </c>
-      <c r="D5" t="str">
-        <v>7816055002</v>
-      </c>
-      <c r="E5" t="str">
-        <v>$2b$10$m0lvsE1PzJIgijPD9hapeulNY8XDz7z7nLCs.jvqNd/ha44o/pQPi</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2025-10-22T04:47:45.393Z</v>
-      </c>
-      <c r="G5" t="str">
-        <v>68f768c7c19182865690172b</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>